--- a/question_bank/MATHS.xlsx
+++ b/question_bank/MATHS.xlsx
@@ -5,24 +5,25 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Backup\D K Patra New\1 IMPORTANT\RKM Admission\PYTHON\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Backup\D K Patra New\1 IMPORTANT\RKM Admission\PYTHON\question_bank\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7500" activeTab="6"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Index" sheetId="2" r:id="rId1"/>
-    <sheet name="Age" sheetId="3" r:id="rId2"/>
-    <sheet name="Percentage" sheetId="1" r:id="rId3"/>
-    <sheet name="Average" sheetId="4" r:id="rId4"/>
-    <sheet name="Unitary Method" sheetId="5" r:id="rId5"/>
-    <sheet name="LCM &amp; HCF" sheetId="6" r:id="rId6"/>
-    <sheet name="LCM &amp; HCF (Guide)" sheetId="7" r:id="rId7"/>
+    <sheet name="Simplification" sheetId="8" r:id="rId2"/>
+    <sheet name="Age" sheetId="3" r:id="rId3"/>
+    <sheet name="Percentage" sheetId="1" r:id="rId4"/>
+    <sheet name="Average" sheetId="4" r:id="rId5"/>
+    <sheet name="Unitary Method" sheetId="5" r:id="rId6"/>
+    <sheet name="LCM &amp; HCF" sheetId="6" r:id="rId7"/>
+    <sheet name="LCM &amp; HCF (Guide)" sheetId="7" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'LCM &amp; HCF'!$A$1:$B$64</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'LCM &amp; HCF (Guide)'!$A$1:$B$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'LCM &amp; HCF'!$A$1:$B$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'LCM &amp; HCF (Guide)'!$A$1:$B$28</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="228">
   <si>
     <t>Questions</t>
   </si>
@@ -933,6 +934,90 @@
   </si>
   <si>
     <t>11; substract the remainder and find HCF</t>
+  </si>
+  <si>
+    <t>12 + 9 ÷ 3</t>
+  </si>
+  <si>
+    <t>16 × 8 ÷ 4</t>
+  </si>
+  <si>
+    <t>23 – 8 × 2</t>
+  </si>
+  <si>
+    <t>32 ÷ 8 + 4 × 6 – 2</t>
+  </si>
+  <si>
+    <t>100 – 72 ÷ 8 + 4 × 3</t>
+  </si>
+  <si>
+    <t>30 + 75 ÷ 15 × 4 – 18</t>
+  </si>
+  <si>
+    <t>8 × 6 + 24 ÷ 6 – 18</t>
+  </si>
+  <si>
+    <t>56 – 36 ÷ 4 × 2 + 7</t>
+  </si>
+  <si>
+    <t>56 ÷ 14 × 3 – 10 ÷ 5 + 1</t>
+  </si>
+  <si>
+    <t>198 – 42 × 15 ÷ 5 + 6</t>
+  </si>
+  <si>
+    <t>105 × 14 ÷ 7 + 6 – 1</t>
+  </si>
+  <si>
+    <t>17 + 34 ÷ 17 × 5 – 20</t>
+  </si>
+  <si>
+    <t>20 – {18 ÷ (7 – 2 + 1)}</t>
+  </si>
+  <si>
+    <t>23 – [6 + { 8 – (9 – 6)}]</t>
+  </si>
+  <si>
+    <t>2[19 – {7 + (12 ÷ 4)}]</t>
+  </si>
+  <si>
+    <t>40 – [12 + {16 – (12 ÷ 3)}]</t>
+  </si>
+  <si>
+    <t>[{(30 – 9 – 6) ÷ 3} × 6 + 6] note: bar above 9-6</t>
+  </si>
+  <si>
+    <t>12 – [6 ÷ 3 + {8 ÷ 2 (8 – 6)}]</t>
+  </si>
+  <si>
+    <t>[40 ÷ {19 – 3(6 – 4 –1)}] note: bar above 4-1</t>
+  </si>
+  <si>
+    <t>[105 ÷ { 23 + 2 (9 – 5 – 2)}] note: bar above 5-2</t>
+  </si>
+  <si>
+    <t>289 + 153 ÷ 17 – 8 × 19</t>
+  </si>
+  <si>
+    <t>7614 + 832 × 48 ÷ 16 – 8</t>
+  </si>
+  <si>
+    <t>7823 – 128 ÷ 16 of 4 – 3973</t>
+  </si>
+  <si>
+    <t>80 + [20 × {20 – (10 ÷ 5)}]</t>
+  </si>
+  <si>
+    <t>[{64 – (12 + 13)} ÷ 3] + 15</t>
+  </si>
+  <si>
+    <t>10 × 10 + [400 ÷ {100 – (50 – 3 × 10)}] note: bar above 3x10</t>
+  </si>
+  <si>
+    <t>Ans</t>
+  </si>
+  <si>
+    <t>Simplify: (ex15 &amp; ex 16 of New Comp. Math)</t>
   </si>
 </sst>
 </file>
@@ -1082,7 +1167,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1180,6 +1265,7 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1512,6 +1598,236 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B27"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="51.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="18" t="s">
+        <v>227</v>
+      </c>
+      <c r="B1" s="18" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>200</v>
+      </c>
+      <c r="B2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>201</v>
+      </c>
+      <c r="B3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>202</v>
+      </c>
+      <c r="B4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>203</v>
+      </c>
+      <c r="B5">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>204</v>
+      </c>
+      <c r="B6">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>205</v>
+      </c>
+      <c r="B7">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>206</v>
+      </c>
+      <c r="B8">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>207</v>
+      </c>
+      <c r="B9">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>208</v>
+      </c>
+      <c r="B10">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>209</v>
+      </c>
+      <c r="B11">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>210</v>
+      </c>
+      <c r="B12">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>211</v>
+      </c>
+      <c r="B13">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="39" t="s">
+        <v>212</v>
+      </c>
+      <c r="B14">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="39" t="s">
+        <v>213</v>
+      </c>
+      <c r="B15">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="39" t="s">
+        <v>214</v>
+      </c>
+      <c r="B16">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="39" t="s">
+        <v>215</v>
+      </c>
+      <c r="B17">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="39" t="s">
+        <v>216</v>
+      </c>
+      <c r="B18">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="39" t="s">
+        <v>217</v>
+      </c>
+      <c r="B19">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="39" t="s">
+        <v>218</v>
+      </c>
+      <c r="B20">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="39" t="s">
+        <v>219</v>
+      </c>
+      <c r="B21">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>220</v>
+      </c>
+      <c r="B22">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>221</v>
+      </c>
+      <c r="B23">
+        <v>10102</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>222</v>
+      </c>
+      <c r="B24">
+        <v>3848</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>223</v>
+      </c>
+      <c r="B25">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>224</v>
+      </c>
+      <c r="B26">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>225</v>
+      </c>
+      <c r="B27">
+        <v>105</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1577,7 +1893,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B16"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
@@ -1723,7 +2039,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1861,7 +2177,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2039,7 +2355,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B64"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2570,7 +2886,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
